--- a/example_run/resolved_bom.xlsx
+++ b/example_run/resolved_bom.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,6 +473,11 @@
           <t>Catalog Description</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Purchase URL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -522,6 +527,7 @@
           <t>Aluminum mounting bracket for NEMA 17 servo motors</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -571,6 +577,7 @@
           <t>Hex socket cap screw, M4 x 12mm, stainless</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -620,6 +627,7 @@
           <t>Right angle planetary gearbox, 20:1 ratio</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -669,6 +677,11 @@
           <t>10-position screw terminal block, 300V rated</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://www.electroconn-example.com/products/TB-100</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -722,6 +735,7 @@
           <t>Linear ball bearing, 6mm bore</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -771,6 +785,11 @@
           <t>24V 5A enclosed switching power supply</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://www.meantech-example.com/shop/PSU-24-5A</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -808,6 +827,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
